--- a/pages/WR_progressions/Men_F200.xlsx
+++ b/pages/WR_progressions/Men_F200.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{865945F0-B5E8-4EF1-89B7-B166AD5FE872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B268A68-1CD3-44AC-92B2-6D85D163ABEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{67FC1AF1-8C25-4294-9519-07881E90C42A}"/>
   </bookViews>
@@ -83,10 +83,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -421,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{130818BB-6E53-4F63-986D-64532D5C2FB3}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="9.9296875" bestFit="1" customWidth="1"/>
@@ -756,7 +757,33 @@
       <c r="J22" s="1"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>9.0909999999999993</v>
+      </c>
+      <c r="B23">
+        <v>9.0909999999999993</v>
+      </c>
+      <c r="C23" s="2">
+        <v>45511</v>
+      </c>
+      <c r="D23" s="3">
+        <v>45511</v>
+      </c>
       <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A24">
+        <v>9.0879999999999992</v>
+      </c>
+      <c r="B24">
+        <v>9.0879999999999992</v>
+      </c>
+      <c r="C24" s="2">
+        <v>45511</v>
+      </c>
+      <c r="D24" s="3">
+        <v>45511</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F3:J24">

--- a/pages/WR_progressions/Men_F200.xlsx
+++ b/pages/WR_progressions/Men_F200.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B268A68-1CD3-44AC-92B2-6D85D163ABEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674DC04D-9822-4AD8-A8E6-7981F3A0C244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{67FC1AF1-8C25-4294-9519-07881E90C42A}"/>
   </bookViews>
@@ -83,11 +83,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -422,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{130818BB-6E53-4F63-986D-64532D5C2FB3}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="9.9296875" bestFit="1" customWidth="1"/>
@@ -766,7 +765,7 @@
       <c r="C23" s="2">
         <v>45511</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23">
         <v>45511</v>
       </c>
       <c r="J23" s="1"/>
@@ -781,8 +780,22 @@
       <c r="C24" s="2">
         <v>45511</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24">
         <v>45511</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A25">
+        <v>8.8569999999999993</v>
+      </c>
+      <c r="B25">
+        <v>8.8569999999999993</v>
+      </c>
+      <c r="C25" s="2">
+        <v>45884</v>
+      </c>
+      <c r="D25">
+        <v>45884</v>
       </c>
     </row>
   </sheetData>
